--- a/data/trans_orig/P36BPD09_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>34084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18003</t>
+          <t>18606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58595</t>
+          <t>58788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378309</t>
+          <t>378779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>430432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>385527</t>
+          <t>385587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>425541</t>
+          <t>426602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>774883</t>
+          <t>774317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>844626</t>
+          <t>842330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>182756</t>
+          <t>182708</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>232546</t>
+          <t>231686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>224854</t>
+          <t>224048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>264318</t>
+          <t>263100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>418901</t>
+          <t>419894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>485804</t>
+          <t>485308</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37026</t>
+          <t>33627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98133</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49586</t>
+          <t>49402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77096</t>
+          <t>76421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>89110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162417</t>
+          <t>161579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>341833</t>
+          <t>315646</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>819240</t>
+          <t>823729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>601844</t>
+          <t>599717</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>650408</t>
+          <t>652675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>869060</t>
+          <t>861974</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1447083</t>
+          <t>1447455</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285286</t>
+          <t>284670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>803561</t>
+          <t>843351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>243975</t>
+          <t>246118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>291686</t>
+          <t>295460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557589</t>
+          <t>554483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1199054</t>
+          <t>1190713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43572</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76222</t>
+          <t>76331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32873</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90502</t>
+          <t>90351</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80092</t>
+          <t>81884</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152620</t>
+          <t>155139</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>412518</t>
+          <t>409007</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>475649</t>
+          <t>469438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251552</t>
+          <t>225445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>594833</t>
+          <t>593343</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>602673</t>
+          <t>603339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1028073</t>
+          <t>1038654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176313</t>
+          <t>179398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233751</t>
+          <t>237541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>253575</t>
+          <t>257665</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>652387</t>
+          <t>673752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>467528</t>
+          <t>460169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>960358</t>
+          <t>949751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72359</t>
+          <t>72903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116171</t>
+          <t>115590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72746</t>
+          <t>72888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111785</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>157209</t>
+          <t>156191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217157</t>
+          <t>217296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>578671</t>
+          <t>577836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>641002</t>
+          <t>641545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>722524</t>
+          <t>723860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>824374</t>
+          <t>822999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1320910</t>
+          <t>1315957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1442496</t>
+          <t>1439131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195502</t>
+          <t>194340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>250289</t>
+          <t>248347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191902</t>
+          <t>189956</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>269900</t>
+          <t>267725</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>405501</t>
+          <t>410713</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>501482</t>
+          <t>508355</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184945</t>
+          <t>179667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283277</t>
+          <t>276971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201327</t>
+          <t>199428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275251</t>
+          <t>277190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>414824</t>
+          <t>417732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536823</t>
+          <t>537790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2662,17 +2662,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2100565</t>
+          <t>2100566</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1641686</t>
+          <t>1627905</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2284010</t>
+          <t>2278571</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1828015</t>
+          <t>1812225</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2400044</t>
+          <t>2403435</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3776327</t>
+          <t>3717717</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4633761</t>
+          <t>4627011</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>916649</t>
+          <t>919853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1649940</t>
+          <t>1629412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>999172</t>
+          <t>997406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1636689</t>
+          <t>1655952</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1968710</t>
+          <t>1974319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2918186</t>
+          <t>2970747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD09_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19333</t>
+          <t>23584</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34084</t>
+          <t>38898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>28899</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>37714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44622</t>
+          <t>52483</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>40225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58788</t>
+          <t>73055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>405143</t>
+          <t>441838</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378779</t>
+          <t>413193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>430432</t>
+          <t>467026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>405051</t>
+          <t>441799</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>385587</t>
+          <t>419751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426602</t>
+          <t>463777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>810194</t>
+          <t>883638</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>774317</t>
+          <t>845709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>842330</t>
+          <t>916751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>207191</t>
+          <t>221290</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>182708</t>
+          <t>194975</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>231686</t>
+          <t>247729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>243841</t>
+          <t>260856</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>224048</t>
+          <t>239748</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>263100</t>
+          <t>283146</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>451032</t>
+          <t>482146</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>419894</t>
+          <t>451570</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>485308</t>
+          <t>518861</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>631667</t>
+          <t>686712</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>631667</t>
+          <t>686712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>631667</t>
+          <t>686712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>674181</t>
+          <t>731555</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>674181</t>
+          <t>731555</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>674181</t>
+          <t>731555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1305848</t>
+          <t>1418267</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1305848</t>
+          <t>1418267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1305848</t>
+          <t>1418267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>68183</t>
+          <t>77441</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>60130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97225</t>
+          <t>100280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61793</t>
+          <t>67769</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49402</t>
+          <t>54720</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76421</t>
+          <t>83346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>129976</t>
+          <t>145210</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>122323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161579</t>
+          <t>172328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>644443</t>
+          <t>703282</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>315646</t>
+          <t>670597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>823729</t>
+          <t>736502</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>626951</t>
+          <t>699416</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>599717</t>
+          <t>672514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>652675</t>
+          <t>726100</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1271393</t>
+          <t>1402698</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>861974</t>
+          <t>1354700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1447455</t>
+          <t>1447692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>480238</t>
+          <t>268194</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>284670</t>
+          <t>237981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>843351</t>
+          <t>300247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>268489</t>
+          <t>302746</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>246118</t>
+          <t>276948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295460</t>
+          <t>329006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>748728</t>
+          <t>570940</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>554483</t>
+          <t>531114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1190713</t>
+          <t>618179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>957233</t>
+          <t>1069931</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>957233</t>
+          <t>1069931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>957233</t>
+          <t>1069931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2150097</t>
+          <t>2118848</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2150097</t>
+          <t>2118848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2150097</t>
+          <t>2118848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58472</t>
+          <t>74978</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43077</t>
+          <t>56775</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76331</t>
+          <t>95495</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64160</t>
+          <t>77279</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29317</t>
+          <t>64220</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90351</t>
+          <t>94944</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>122632</t>
+          <t>152257</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81884</t>
+          <t>129186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155139</t>
+          <t>179553</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>441290</t>
+          <t>494929</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>409007</t>
+          <t>461594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>469438</t>
+          <t>525829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>447530</t>
+          <t>522894</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>225445</t>
+          <t>496644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>593343</t>
+          <t>547979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>888820</t>
+          <t>1017823</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>603339</t>
+          <t>973988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1038654</t>
+          <t>1056293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>204918</t>
+          <t>233166</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179398</t>
+          <t>200633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237541</t>
+          <t>263296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>421676</t>
+          <t>212086</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257665</t>
+          <t>189866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>673752</t>
+          <t>236404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>626594</t>
+          <t>445252</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>460169</t>
+          <t>409226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>949751</t>
+          <t>484731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>93093</t>
+          <t>97710</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72903</t>
+          <t>78954</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115590</t>
+          <t>119595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>92954</t>
+          <t>107094</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72888</t>
+          <t>88195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>126885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>186046</t>
+          <t>204803</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156191</t>
+          <t>178526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217296</t>
+          <t>235013</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>609689</t>
+          <t>646352</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>577836</t>
+          <t>614401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>641545</t>
+          <t>676188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>758149</t>
+          <t>747842</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>723860</t>
+          <t>718449</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>822999</t>
+          <t>775109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1367838</t>
+          <t>1394195</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1315957</t>
+          <t>1348588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1439131</t>
+          <t>1436085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>222426</t>
+          <t>244390</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194340</t>
+          <t>215906</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>248347</t>
+          <t>274621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>239230</t>
+          <t>259522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>189956</t>
+          <t>236872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>267725</t>
+          <t>286080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>461656</t>
+          <t>503912</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>410713</t>
+          <t>467457</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>508355</t>
+          <t>544671</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925208</t>
+          <t>988452</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925208</t>
+          <t>988452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925208</t>
+          <t>988452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1090332</t>
+          <t>1114458</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1090332</t>
+          <t>1114458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1090332</t>
+          <t>1114458</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2015540</t>
+          <t>2102910</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2015540</t>
+          <t>2102910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2015540</t>
+          <t>2102910</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239080</t>
+          <t>273713</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179667</t>
+          <t>233941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276971</t>
+          <t>310406</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>244195</t>
+          <t>281041</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>199428</t>
+          <t>251397</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277190</t>
+          <t>313255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>483276</t>
+          <t>554754</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>417732</t>
+          <t>502716</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>537790</t>
+          <t>603391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2100566</t>
+          <t>2286401</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1627905</t>
+          <t>2222416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2278571</t>
+          <t>2346394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2237680</t>
+          <t>2411951</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1812225</t>
+          <t>2358902</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2403435</t>
+          <t>2463660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4338246</t>
+          <t>4698353</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3717717</t>
+          <t>4616737</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4627011</t>
+          <t>4780572</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1114774</t>
+          <t>967040</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>919853</t>
+          <t>907373</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1629412</t>
+          <t>1031330</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1173237</t>
+          <t>1035210</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>997406</t>
+          <t>988178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1655952</t>
+          <t>1083488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2288011</t>
+          <t>2002250</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1974319</t>
+          <t>1929276</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2970747</t>
+          <t>2078546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
